--- a/artfynd/A 24563-2022 artfynd.xlsx
+++ b/artfynd/A 24563-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24563-2022 artfynd.xlsx
+++ b/artfynd/A 24563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56164547</v>
+        <v>60793977</v>
       </c>
       <c r="B2" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232138</v>
+        <v>2058</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691682.6220663623</v>
+        <v>691747</v>
       </c>
       <c r="R2" t="n">
-        <v>6682947.071242041</v>
+        <v>6683022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca. 100 ex. under gran i äldre, beteshävdad barrskog.</t>
+          <t>3 ex. i äldre, beteshävdad barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,19 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60793977</v>
+        <v>60793978</v>
       </c>
       <c r="B3" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691746.9823095853</v>
+        <v>691686</v>
       </c>
       <c r="R3" t="n">
-        <v>6683021.59995384</v>
+        <v>6683056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,24 +868,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3 ex. i äldre, beteshävdad barrskog.</t>
+          <t>Ca. 20 ex. i äldre, beteshävdad barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,59 +907,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60793978</v>
+        <v>75873400</v>
       </c>
       <c r="B4" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Strömsängen 1,5 km VNV om Tuskö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691686.3833792241</v>
+        <v>691676</v>
       </c>
       <c r="R4" t="n">
-        <v>6683055.730949699</v>
+        <v>6683047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,24 +975,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca. 20 ex. i äldre, beteshävdad barrskog.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,11 +993,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre, beteshävdad barrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1068,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69517681</v>
+        <v>69507144</v>
       </c>
       <c r="B5" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,26 +1020,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4189</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691776.3628617101</v>
+        <v>691673</v>
       </c>
       <c r="R5" t="n">
-        <v>6683059.960977651</v>
+        <v>6682947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,24 +1086,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 fjolårs-ex. i äldre, beteshävdad barrskog.</t>
+          <t>Ca. 10 ex.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,11 +1104,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre, beteshävdad barrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1202,12 +1123,7 @@
         <v>69510802</v>
       </c>
       <c r="B6" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691796.3985224206</v>
+        <v>691796</v>
       </c>
       <c r="R6" t="n">
-        <v>6683058.02880062</v>
+        <v>6683058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,19 +1197,9 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2005-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1330,15 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69517680</v>
+        <v>69510803</v>
       </c>
       <c r="B7" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,26 +1247,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4189</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1379,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691755.8154764172</v>
+        <v>691682</v>
       </c>
       <c r="R7" t="n">
-        <v>6683128.534221579</v>
+        <v>6683026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,24 +1313,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2 fjolårs-ex. i äldre, beteshävdad barrskog.</t>
+          <t>Ca. 10 ex. i äldre, beteshävdad barrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,15 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69510803</v>
+        <v>69517680</v>
       </c>
       <c r="B8" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,26 +1363,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>4189</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1510,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691681.9832963163</v>
+        <v>691756</v>
       </c>
       <c r="R8" t="n">
-        <v>6683025.648179539</v>
+        <v>6683129</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,24 +1429,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca. 10 ex. i äldre, beteshävdad barrskog.</t>
+          <t>2 fjolårs-ex. i äldre, beteshävdad barrskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1592,15 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75873400</v>
+        <v>69517681</v>
       </c>
       <c r="B9" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,34 +1479,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>4189</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strömsängen 1,5 km VNV om Tuskö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691676.3898228158</v>
+        <v>691776</v>
       </c>
       <c r="R9" t="n">
-        <v>6683046.748081241</v>
+        <v>6683060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,24 +1545,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>1 fjolårs-ex. i äldre, beteshävdad barrskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1693,6 +1563,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre, beteshävdad barrskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1706,6 +1581,238 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>56164547</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strömsängen 1,5 km VNV om Tuskö, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>691683</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6682947</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2005-09-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2005-09-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca. 100 ex. under gran i äldre, beteshävdad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre, beteshävdad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>56164548</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strömsängen 1,5 km VNV om Tuskö, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691659</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6682970</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2005-09-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2005-09-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca. 200 ex. under gran i äldre, beteshävdad barrskog. Sporer amyloida.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre, beteshävdad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24563-2022 artfynd.xlsx
+++ b/artfynd/A 24563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60793977</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60793978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75873400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69507144</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510802</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510803</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69517681</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164547</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164548</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1813,8 +1863,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69517680</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>